--- a/EG1A.xlsx
+++ b/EG1A.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="62">
   <si>
     <t/>
   </si>
   <si>
-    <t>10004884</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT CHO 950</t>
+    <t>20027166</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP220</t>
   </si>
   <si>
     <t>EG1A</t>
@@ -28,111 +28,96 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20103297</t>
+  </si>
+  <si>
+    <t>IDM FAC.TISSUE NP200</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20083529</t>
+  </si>
+  <si>
+    <t>HAPPY TOS SEAWEED 52</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>10005909</t>
-  </si>
-  <si>
-    <t>INDOMILK UHT PLN 950</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20014069</t>
-  </si>
-  <si>
-    <t>FF UHT FULL CRM 946</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20014071</t>
-  </si>
-  <si>
-    <t>FF UHT CHOCO 946ML</t>
+    <t>20087713</t>
+  </si>
+  <si>
+    <t>IDM NDL AYM PDS 90G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20103718</t>
-  </si>
-  <si>
-    <t>TJH KURMA SUSU KR189</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10029542</t>
+  </si>
+  <si>
+    <t>MR.BREAD COKLAT KEJU</t>
+  </si>
+  <si>
+    <t>RT,(E-1H)</t>
+  </si>
+  <si>
+    <t>20139577</t>
+  </si>
+  <si>
+    <t>PC AREN LATTE 210ML</t>
+  </si>
+  <si>
+    <t>20139578</t>
+  </si>
+  <si>
+    <t>PC GOLDN CARAMEL 210</t>
+  </si>
+  <si>
+    <t>20020008</t>
+  </si>
+  <si>
+    <t>MR.BREAD MANIS CHO 4</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG COKLT TPK 225</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20054589</t>
-  </si>
-  <si>
-    <t>3SAPI KRIMER 490G</t>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STRWB TPK 225</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20125783</t>
-  </si>
-  <si>
-    <t>CAP/ENAK KKM PTH 535</t>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/F FULL CRM TPK 225</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>10029536</t>
-  </si>
-  <si>
-    <t>MR.BREAD TAWAR</t>
-  </si>
-  <si>
-    <t>RT,(E-1H)</t>
-  </si>
-  <si>
-    <t>20118115</t>
-  </si>
-  <si>
-    <t>FRISIAN FLAG PTH 240</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20112945</t>
-  </si>
-  <si>
-    <t>FF SKM COKLAT 240G</t>
-  </si>
-  <si>
-    <t>20141099</t>
-  </si>
-  <si>
-    <t>FF CRMY GULA ARN 240</t>
-  </si>
-  <si>
-    <t>20020008</t>
-  </si>
-  <si>
-    <t>MR.BREAD MANIS CHO 4</t>
-  </si>
-  <si>
-    <t>20035484</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH MLATI350</t>
-  </si>
-  <si>
-    <t>20048155</t>
-  </si>
-  <si>
-    <t>PUCUK/H TEH L/SGR350</t>
-  </si>
-  <si>
     <t>20141062</t>
   </si>
   <si>
@@ -160,76 +145,58 @@
     <t>S/Q CHOCO ALMOND 52G</t>
   </si>
   <si>
-    <t>10016646</t>
-  </si>
-  <si>
-    <t>INDO/F KECAP MN.R725</t>
-  </si>
-  <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20027097</t>
-  </si>
-  <si>
-    <t>INDOFOOD SMBL EXT275</t>
-  </si>
-  <si>
-    <t>20015850</t>
-  </si>
-  <si>
-    <t>INDOFOOD SBL PDS 275</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
+    <t>20092857</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 130</t>
+  </si>
+  <si>
+    <t>20119460</t>
+  </si>
+  <si>
+    <t>POTABEE SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20122571</t>
+  </si>
+  <si>
+    <t>PIATTOS SAPI PG 120G</t>
   </si>
   <si>
     <t>RT,(E-2B)</t>
   </si>
   <si>
-    <t>10000652</t>
-  </si>
-  <si>
-    <t>INDOMI AYAM BWNG 69G</t>
-  </si>
-  <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
-  </si>
-  <si>
-    <t>20138739</t>
-  </si>
-  <si>
-    <t>I/POP SPGTI BGLN 84G</t>
-  </si>
-  <si>
-    <t>10000975</t>
-  </si>
-  <si>
-    <t>POP MIE AYAM 75G</t>
-  </si>
-  <si>
-    <t>20136587</t>
-  </si>
-  <si>
-    <t>POP MI INDOMIE GR 80</t>
-  </si>
-  <si>
-    <t>20084481</t>
-  </si>
-  <si>
-    <t>POP MIE PD.DWR AYM75</t>
-  </si>
-  <si>
-    <t>20131530</t>
-  </si>
-  <si>
-    <t>POP MI TORI MISO 77G</t>
+    <t>20098348</t>
+  </si>
+  <si>
+    <t>REBO KUACI ORIGNL120</t>
+  </si>
+  <si>
+    <t>20015337</t>
+  </si>
+  <si>
+    <t>LEXUS SANDW COKL 190</t>
+  </si>
+  <si>
+    <t>20133506</t>
+  </si>
+  <si>
+    <t>DELFI KRICE SWET64.8</t>
+  </si>
+  <si>
+    <t>20134969</t>
+  </si>
+  <si>
+    <t>MILO SANDW MILK 104G</t>
+  </si>
+  <si>
+    <t>20138261</t>
+  </si>
+  <si>
+    <t>POCKY BLUEBERRY 38G</t>
   </si>
 </sst>
 </file>
@@ -622,14 +589,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -709,15 +676,15 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -726,70 +693,70 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -806,50 +773,50 @@
         <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -866,78 +833,78 @@
         <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -946,107 +913,107 @@
         <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>51</v>
@@ -1054,182 +1021,62 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
